--- a/data/processed/regraded_routes.xlsx
+++ b/data/processed/regraded_routes.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T87"/>
+  <dimension ref="A1:U88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,45 +478,50 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>suggested_grade_source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>grade_clean</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>grade_order</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>is_multipitch</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>yds</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>first_ascent</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>first_ascent_year</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>suggested_clean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>suggested_order</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
@@ -574,37 +579,38 @@
           <t>8a</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>8a+</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>26</v>
       </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5.13c</t>
         </is>
       </c>
-      <c r="P2" s="1" t="n">
+      <c r="Q2" s="1" t="n">
         <v>38909</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>2006</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>8a</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>25</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -662,37 +668,38 @@
           <t>8a</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>8a+</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>26</v>
       </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>5.13c</t>
         </is>
       </c>
-      <c r="P3" s="1" t="n">
+      <c r="Q3" s="1" t="n">
         <v>45621</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>2024</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>8a</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>25</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -750,37 +757,38 @@
           <t>8a+</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>27</v>
       </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>5.13d</t>
         </is>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="Q4" s="1" t="n">
         <v>34608</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1994</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>8a+</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>26</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -838,37 +846,38 @@
           <t>8a+</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>27</v>
       </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>5.13d</t>
         </is>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="Q5" s="1" t="n">
         <v>37104</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>2001</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>8a+</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>26</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -926,37 +935,38 @@
           <t>8a+</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>27</v>
       </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>5.13d</t>
         </is>
       </c>
-      <c r="P6" s="1" t="n">
+      <c r="Q6" s="1" t="n">
         <v>37257</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>2002</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>8a+</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>26</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -1014,37 +1024,38 @@
           <t>8a+/8b</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>27</v>
       </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>5.13d</t>
         </is>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="Q7" s="1" t="n">
         <v>45620</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>2024</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>8a+</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>26</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -1102,37 +1113,38 @@
           <t>8b</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>28</v>
       </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>5.14a</t>
         </is>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="Q8" s="1" t="n">
         <v>32173</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>1988</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>27</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -1190,37 +1202,38 @@
           <t>8b</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>28</v>
       </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>5.14a</t>
         </is>
       </c>
-      <c r="P9" s="1" t="n">
+      <c r="Q9" s="1" t="n">
         <v>32509</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1989</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>27</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -1278,37 +1291,38 @@
           <t>8b</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>8a+</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>26</v>
       </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>5.13c</t>
         </is>
       </c>
-      <c r="P10" s="1" t="n">
+      <c r="Q10" s="1" t="n">
         <v>33239</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>1991</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>27</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -1366,37 +1380,38 @@
           <t>8b</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>28</v>
       </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>5.14a</t>
         </is>
       </c>
-      <c r="P11" s="1" t="n">
+      <c r="Q11" s="1" t="n">
         <v>34418</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>1994</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>27</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -1454,37 +1469,38 @@
           <t>8b/8b+</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>8a+</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>26</v>
       </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>5.13c</t>
         </is>
       </c>
-      <c r="P12" s="1" t="n">
+      <c r="Q12" s="1" t="n">
         <v>35796</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>1998</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>27</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -1542,37 +1558,38 @@
           <t>8b</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>8a+</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>26</v>
       </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>5.13c</t>
         </is>
       </c>
-      <c r="P13" s="1" t="n">
+      <c r="Q13" s="1" t="n">
         <v>43101</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>2018</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>27</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -1630,37 +1647,38 @@
           <t>8b+</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>29</v>
       </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P14" s="1" t="n">
+      <c r="Q14" s="1" t="n">
         <v>32143</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>1988</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>28</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -1718,37 +1736,38 @@
           <t>8b+</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>29</v>
       </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P15" s="1" t="n">
+      <c r="Q15" s="1" t="n">
         <v>37622</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>2003</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>28</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -1806,37 +1825,38 @@
           <t>8b+</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>29</v>
       </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P16" s="1" t="n">
+      <c r="Q16" s="1" t="n">
         <v>39202</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>2007</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>28</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -1894,37 +1914,38 @@
           <t>8b+/8c</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>29</v>
       </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P17" s="1" t="n">
+      <c r="Q17" s="1" t="n">
         <v>39555</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>2008</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>28</v>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -1982,37 +2003,38 @@
           <t>8b+</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>29</v>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P18" s="1" t="n">
+      <c r="Q18" s="1" t="n">
         <v>39635</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>2008</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>28</v>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2070,37 +2092,38 @@
           <t>8b+/8c</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>29</v>
       </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P19" s="1" t="n">
+      <c r="Q19" s="1" t="n">
         <v>39711</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>2008</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>28</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2158,37 +2181,38 @@
           <t>8b+ (hard)</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>29</v>
       </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P20" s="1" t="n">
+      <c r="Q20" s="1" t="n">
         <v>40344</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>2010</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>28</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2246,37 +2270,38 @@
           <t>8b+</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>29</v>
       </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P21" s="1" t="n">
+      <c r="Q21" s="1" t="n">
         <v>41492</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>2013</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>28</v>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2334,37 +2359,38 @@
           <t>8b+/8c</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>29</v>
       </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P22" s="1" t="n">
+      <c r="Q22" s="1" t="n">
         <v>44619</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>2022</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>28</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2422,37 +2448,38 @@
           <t>8c</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>30</v>
       </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P23" s="1" t="n">
+      <c r="Q23" s="1" t="n">
         <v>32962</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>1990</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>29</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2510,37 +2537,38 @@
           <t>8c</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>30</v>
       </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P24" s="1" t="n">
+      <c r="Q24" s="1" t="n">
         <v>34700</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>1995</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>29</v>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2598,37 +2626,38 @@
           <t>8c</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>28</v>
       </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>5.14a</t>
         </is>
       </c>
-      <c r="P25" s="1" t="n">
+      <c r="Q25" s="1" t="n">
         <v>34820</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>1995</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>29</v>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -2682,37 +2711,38 @@
           <t>8c</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>30</v>
       </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P26" s="1" t="n">
+      <c r="Q26" s="1" t="n">
         <v>36892</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>2001</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>29</v>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2770,37 +2800,38 @@
           <t>8c</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>30</v>
       </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P27" s="1" t="n">
+      <c r="Q27" s="1" t="n">
         <v>37399</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>2002</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>29</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2858,37 +2889,38 @@
           <t>8c</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>30</v>
       </c>
-      <c r="N28" t="b">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P28" s="1" t="n">
+      <c r="Q28" s="1" t="n">
         <v>37834</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>2003</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>29</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -2946,37 +2978,38 @@
           <t>8c</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>30</v>
       </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P29" s="1" t="n">
+      <c r="Q29" s="1" t="n">
         <v>38215</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>2004</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>29</v>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3034,37 +3067,38 @@
           <t>8c/8c+</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>31</v>
       </c>
-      <c r="N30" t="b">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P30" s="1" t="n">
+      <c r="Q30" s="1" t="n">
         <v>38872</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>2006</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>29</v>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3122,37 +3156,38 @@
           <t>8c</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>31</v>
       </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P31" s="1" t="n">
+      <c r="Q31" s="1" t="n">
         <v>39606</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2008</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>29</v>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3210,37 +3245,38 @@
           <t>8c</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
         <is>
           <t>8b+</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>28</v>
       </c>
-      <c r="N32" t="b">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>5.14a</t>
         </is>
       </c>
-      <c r="P32" s="1" t="n">
+      <c r="Q32" s="1" t="n">
         <v>41887</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>2014</v>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>29</v>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -3298,37 +3334,38 @@
           <t>8c/8c+</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>30</v>
       </c>
-      <c r="N33" t="b">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P33" s="1" t="n">
+      <c r="Q33" s="1" t="n">
         <v>44027</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>2020</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>29</v>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3386,37 +3423,38 @@
           <t>8c/8c+</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>30</v>
       </c>
-      <c r="N34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P34" s="1" t="n">
+      <c r="Q34" s="1" t="n">
         <v>46166</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>2026</v>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>29</v>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3474,37 +3512,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>31</v>
       </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P35" s="1" t="n">
+      <c r="Q35" s="1" t="n">
         <v>33038</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>1990</v>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>30</v>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3562,37 +3601,38 @@
           <t>8c+/9a</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>32</v>
       </c>
-      <c r="N36" t="b">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P36" s="1" t="n">
+      <c r="Q36" s="1" t="n">
         <v>35065</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>1996</v>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>30</v>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3650,37 +3690,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>31</v>
       </c>
-      <c r="N37" t="b">
-        <v>0</v>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P37" s="1" t="n">
+      <c r="Q37" s="1" t="n">
         <v>37114</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>2001</v>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>30</v>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3738,37 +3779,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>31</v>
       </c>
-      <c r="N38" t="b">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P38" s="1" t="n">
+      <c r="Q38" s="1" t="n">
         <v>39531</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>2008</v>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>30</v>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3826,37 +3868,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>31</v>
       </c>
-      <c r="N39" t="b">
-        <v>0</v>
-      </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P39" s="1" t="n">
+      <c r="Q39" s="1" t="n">
         <v>39531</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>2008</v>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>30</v>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -3914,37 +3957,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>32</v>
       </c>
-      <c r="N40" t="b">
-        <v>0</v>
-      </c>
-      <c r="O40" t="inlineStr">
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P40" s="1" t="n">
+      <c r="Q40" s="1" t="n">
         <v>39683</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>2008</v>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>30</v>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -4002,37 +4046,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>31</v>
       </c>
-      <c r="N41" t="b">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr">
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P41" s="1" t="n">
+      <c r="Q41" s="1" t="n">
         <v>39693</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>2008</v>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>30</v>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -4090,37 +4135,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>31</v>
       </c>
-      <c r="N42" t="b">
-        <v>0</v>
-      </c>
-      <c r="O42" t="inlineStr">
+      <c r="O42" t="b">
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P42" s="1" t="n">
+      <c r="Q42" s="1" t="n">
         <v>39711</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2008</v>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>30</v>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -4178,37 +4224,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>31</v>
       </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P43" s="1" t="n">
+      <c r="Q43" s="1" t="n">
         <v>39814</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>2009</v>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>30</v>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -4266,37 +4313,38 @@
           <t>8c+ (soft)</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>29</v>
       </c>
-      <c r="N44" t="b">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P44" s="1" t="n">
+      <c r="Q44" s="1" t="n">
         <v>41100</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>2012</v>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>30</v>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -4354,37 +4402,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>29</v>
       </c>
-      <c r="N45" t="b">
-        <v>0</v>
-      </c>
-      <c r="O45" t="inlineStr">
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P45" s="1" t="n">
+      <c r="Q45" s="1" t="n">
         <v>42247</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>2015</v>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>30</v>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -4442,37 +4491,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>31</v>
       </c>
-      <c r="N46" t="b">
-        <v>0</v>
-      </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" t="b">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P46" s="1" t="n">
+      <c r="Q46" s="1" t="n">
         <v>43201</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>2018</v>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>30</v>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -4530,37 +4580,38 @@
           <t>8c+/9a</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>31</v>
       </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
-      <c r="O47" t="inlineStr">
+      <c r="O47" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P47" s="1" t="n">
+      <c r="Q47" s="1" t="n">
         <v>43419</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>2018</v>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>30</v>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -4618,37 +4669,38 @@
           <t>8c+/9a</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>31</v>
       </c>
-      <c r="N48" t="b">
-        <v>0</v>
-      </c>
-      <c r="O48" t="inlineStr">
+      <c r="O48" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P48" s="1" t="n">
+      <c r="Q48" s="1" t="n">
         <v>43494</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>2019</v>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>30</v>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -4706,37 +4758,38 @@
           <t>8c+ (soft)</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>29</v>
       </c>
-      <c r="N49" t="b">
-        <v>0</v>
-      </c>
-      <c r="O49" t="inlineStr">
+      <c r="O49" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P49" s="1" t="n">
+      <c r="Q49" s="1" t="n">
         <v>43526</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>2019</v>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>30</v>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -4794,37 +4847,38 @@
           <t>8c+</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>29</v>
       </c>
-      <c r="N50" t="b">
-        <v>0</v>
-      </c>
-      <c r="O50" t="inlineStr">
+      <c r="O50" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P50" s="1" t="n">
+      <c r="Q50" s="1" t="n">
         <v>44005</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>2020</v>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>30</v>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -4882,37 +4936,38 @@
           <t>8c+/9a</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>31</v>
       </c>
-      <c r="N51" t="b">
-        <v>0</v>
-      </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P51" s="1" t="n">
+      <c r="Q51" s="1" t="n">
         <v>44322</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>2021</v>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>30</v>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -4970,37 +5025,38 @@
           <t>8c+/9a</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>31</v>
       </c>
-      <c r="N52" t="b">
-        <v>0</v>
-      </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P52" s="1" t="n">
+      <c r="Q52" s="1" t="n">
         <v>45873</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>2025</v>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>30</v>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -5058,37 +5114,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>32</v>
       </c>
-      <c r="N53" t="b">
-        <v>0</v>
-      </c>
-      <c r="O53" t="inlineStr">
+      <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P53" s="1" t="n">
+      <c r="Q53" s="1" t="n">
         <v>35405</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>1996</v>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>31</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -5146,37 +5203,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>32</v>
       </c>
-      <c r="N54" t="b">
-        <v>0</v>
-      </c>
-      <c r="O54" t="inlineStr">
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P54" s="1" t="n">
+      <c r="Q54" s="1" t="n">
         <v>36082</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>1998</v>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>31</v>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -5234,37 +5292,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>32</v>
       </c>
-      <c r="N55" t="b">
-        <v>0</v>
-      </c>
-      <c r="O55" t="inlineStr">
+      <c r="O55" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P55" s="1" t="n">
+      <c r="Q55" s="1" t="n">
         <v>37386</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>2002</v>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>31</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -5322,37 +5381,38 @@
           <t>9a/9a+</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>32</v>
       </c>
-      <c r="N56" t="b">
-        <v>0</v>
-      </c>
-      <c r="O56" t="inlineStr">
+      <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P56" s="1" t="n">
+      <c r="Q56" s="1" t="n">
         <v>38047</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>2004</v>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>31</v>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -5410,37 +5470,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
         <is>
           <t>8c</t>
         </is>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>29</v>
       </c>
-      <c r="N57" t="b">
-        <v>0</v>
-      </c>
-      <c r="O57" t="inlineStr">
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t>5.14b</t>
         </is>
       </c>
-      <c r="P57" s="1" t="n">
+      <c r="Q57" s="1" t="n">
         <v>39000</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>2006</v>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>31</v>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -5498,37 +5559,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>32</v>
       </c>
-      <c r="N58" t="b">
-        <v>0</v>
-      </c>
-      <c r="O58" t="inlineStr">
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P58" s="1" t="n">
+      <c r="Q58" s="1" t="n">
         <v>39278</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>2007</v>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>31</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -5586,37 +5648,38 @@
           <t>9a/9a+</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>32</v>
       </c>
-      <c r="N59" t="b">
-        <v>0</v>
-      </c>
-      <c r="O59" t="inlineStr">
+      <c r="O59" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P59" s="1" t="n">
+      <c r="Q59" s="1" t="n">
         <v>39960</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>2009</v>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>31</v>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -5674,37 +5737,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>32</v>
       </c>
-      <c r="N60" t="b">
-        <v>0</v>
-      </c>
-      <c r="O60" t="inlineStr">
+      <c r="O60" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P60" s="1" t="n">
+      <c r="Q60" s="1" t="n">
         <v>40049</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>2009</v>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>31</v>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -5762,37 +5826,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>32</v>
       </c>
-      <c r="N61" t="b">
-        <v>0</v>
-      </c>
-      <c r="O61" t="inlineStr">
+      <c r="O61" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P61" s="1" t="n">
+      <c r="Q61" s="1" t="n">
         <v>40274</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="R61" t="n">
         <v>2010</v>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S61" t="n">
+      <c r="T61" t="n">
         <v>31</v>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -5850,37 +5915,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>30</v>
       </c>
-      <c r="N62" t="b">
-        <v>0</v>
-      </c>
-      <c r="O62" t="inlineStr">
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P62" s="1" t="n">
+      <c r="Q62" s="1" t="n">
         <v>40909</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="R62" t="n">
         <v>2012</v>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S62" t="n">
+      <c r="T62" t="n">
         <v>31</v>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -5938,37 +6004,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>32</v>
       </c>
-      <c r="N63" t="b">
-        <v>0</v>
-      </c>
-      <c r="O63" t="inlineStr">
+      <c r="O63" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P63" s="1" t="n">
+      <c r="Q63" s="1" t="n">
         <v>41481</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="R63" t="n">
         <v>2013</v>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S63" t="n">
+      <c r="T63" t="n">
         <v>31</v>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -6026,37 +6093,38 @@
           <t>9a (hard)</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>32</v>
       </c>
-      <c r="N64" t="b">
-        <v>0</v>
-      </c>
-      <c r="O64" t="inlineStr">
+      <c r="O64" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P64" s="1" t="n">
+      <c r="Q64" s="1" t="n">
         <v>42325</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="R64" t="n">
         <v>2015</v>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S64" t="n">
+      <c r="T64" t="n">
         <v>31</v>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -6114,37 +6182,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>30</v>
       </c>
-      <c r="N65" t="b">
-        <v>0</v>
-      </c>
-      <c r="O65" t="inlineStr">
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P65" s="1" t="n">
+      <c r="Q65" s="1" t="n">
         <v>42659</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="R65" t="n">
         <v>2016</v>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S65" t="n">
+      <c r="T65" t="n">
         <v>31</v>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -6202,37 +6271,38 @@
           <t>9a/9a+</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>32</v>
       </c>
-      <c r="N66" t="b">
-        <v>0</v>
-      </c>
-      <c r="O66" t="inlineStr">
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P66" s="1" t="n">
+      <c r="Q66" s="1" t="n">
         <v>42671</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="R66" t="n">
         <v>2016</v>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S66" t="n">
+      <c r="T66" t="n">
         <v>31</v>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -6290,37 +6360,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>32</v>
       </c>
-      <c r="N67" t="b">
-        <v>0</v>
-      </c>
-      <c r="O67" t="inlineStr">
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P67" s="1" t="n">
+      <c r="Q67" s="1" t="n">
         <v>43611</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="R67" t="n">
         <v>2019</v>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S67" t="n">
+      <c r="T67" t="n">
         <v>31</v>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -6378,37 +6449,38 @@
           <t>9a</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
         <v>30</v>
       </c>
-      <c r="N68" t="b">
-        <v>0</v>
-      </c>
-      <c r="O68" t="inlineStr">
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P68" s="1" t="n">
+      <c r="Q68" s="1" t="n">
         <v>44685</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="R68" t="n">
         <v>2022</v>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S68" t="n">
+      <c r="T68" t="n">
         <v>31</v>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -6466,37 +6538,38 @@
           <t>9a/9a+</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>32</v>
       </c>
-      <c r="N69" t="b">
-        <v>0</v>
-      </c>
-      <c r="O69" t="inlineStr">
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P69" s="1" t="n">
+      <c r="Q69" s="1" t="n">
         <v>45169</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="R69" t="n">
         <v>2023</v>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="S69" t="n">
+      <c r="T69" t="n">
         <v>31</v>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -6554,37 +6627,38 @@
           <t>9a+</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
         <v>31</v>
       </c>
-      <c r="N70" t="b">
-        <v>0</v>
-      </c>
-      <c r="O70" t="inlineStr">
+      <c r="O70" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P70" s="1" t="n">
+      <c r="Q70" s="1" t="n">
         <v>38656</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="R70" t="n">
         <v>2005</v>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="S70" t="n">
+      <c r="T70" t="n">
         <v>32</v>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -6642,37 +6716,38 @@
           <t>9a+</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>31</v>
       </c>
-      <c r="N71" t="b">
-        <v>0</v>
-      </c>
-      <c r="O71" t="inlineStr">
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P71" s="1" t="n">
+      <c r="Q71" s="1" t="n">
         <v>40133</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="R71" t="n">
         <v>2009</v>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="S71" t="n">
+      <c r="T71" t="n">
         <v>32</v>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -6730,37 +6805,38 @@
           <t>9a+</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>31</v>
       </c>
-      <c r="N72" t="b">
-        <v>0</v>
-      </c>
-      <c r="O72" t="inlineStr">
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P72" s="1" t="n">
+      <c r="Q72" s="1" t="n">
         <v>40846</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="R72" t="n">
         <v>2011</v>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="S72" t="n">
+      <c r="T72" t="n">
         <v>32</v>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -6818,37 +6894,38 @@
           <t>9a+</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>33</v>
       </c>
-      <c r="N73" t="b">
-        <v>0</v>
-      </c>
-      <c r="O73" t="inlineStr">
+      <c r="O73" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr">
         <is>
           <t>5.15b</t>
         </is>
       </c>
-      <c r="P73" s="1" t="n">
+      <c r="Q73" s="1" t="n">
         <v>41548</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="R73" t="n">
         <v>2013</v>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="S73" t="n">
+      <c r="T73" t="n">
         <v>32</v>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -6906,37 +6983,38 @@
           <t>9a+</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
         <v>33</v>
       </c>
-      <c r="N74" t="b">
-        <v>0</v>
-      </c>
-      <c r="O74" t="inlineStr">
+      <c r="O74" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t>5.15b</t>
         </is>
       </c>
-      <c r="P74" s="1" t="n">
+      <c r="Q74" s="1" t="n">
         <v>42903</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="R74" t="n">
         <v>2017</v>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="S74" t="n">
+      <c r="T74" t="n">
         <v>32</v>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -6994,37 +7072,38 @@
           <t>9a+/9b</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
         <v>31</v>
       </c>
-      <c r="N75" t="b">
-        <v>0</v>
-      </c>
-      <c r="O75" t="inlineStr">
+      <c r="O75" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P75" s="1" t="n">
+      <c r="Q75" s="1" t="n">
         <v>43830</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="R75" t="n">
         <v>2019</v>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="S75" t="n">
+      <c r="T75" t="n">
         <v>32</v>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7082,37 +7161,38 @@
           <t>9a+</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
         <v>31</v>
       </c>
-      <c r="N76" t="b">
-        <v>0</v>
-      </c>
-      <c r="O76" t="inlineStr">
+      <c r="O76" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P76" s="1" t="n">
+      <c r="Q76" s="1" t="n">
         <v>43862</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="R76" t="n">
         <v>2020</v>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="S76" t="n">
+      <c r="T76" t="n">
         <v>32</v>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7170,37 +7250,38 @@
           <t>9a+</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
         <is>
           <t>8c+</t>
         </is>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
         <v>30</v>
       </c>
-      <c r="N77" t="b">
-        <v>0</v>
-      </c>
-      <c r="O77" t="inlineStr">
+      <c r="O77" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr">
         <is>
           <t>5.14c</t>
         </is>
       </c>
-      <c r="P77" s="1" t="n">
+      <c r="Q77" s="1" t="n">
         <v>44119</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="R77" t="n">
         <v>2020</v>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="S77" t="n">
+      <c r="T77" t="n">
         <v>32</v>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7258,37 +7339,38 @@
           <t>9a+</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M78" t="n">
+      <c r="N78" t="n">
         <v>31</v>
       </c>
-      <c r="N78" t="b">
-        <v>0</v>
-      </c>
-      <c r="O78" t="inlineStr">
+      <c r="O78" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P78" s="1" t="n">
+      <c r="Q78" s="1" t="n">
         <v>45214</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="R78" t="n">
         <v>2023</v>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="S78" t="n">
+      <c r="T78" t="n">
         <v>32</v>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7346,37 +7428,38 @@
           <t>9b</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
         <v>31</v>
       </c>
-      <c r="N79" t="b">
-        <v>0</v>
-      </c>
-      <c r="O79" t="inlineStr">
+      <c r="O79" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P79" s="1" t="n">
+      <c r="Q79" s="1" t="n">
         <v>34856</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="R79" t="n">
         <v>1995</v>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="S79" t="n">
+      <c r="T79" t="n">
         <v>33</v>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7434,37 +7517,38 @@
           <t>9b</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
         <v>32</v>
       </c>
-      <c r="N80" t="b">
-        <v>0</v>
-      </c>
-      <c r="O80" t="inlineStr">
+      <c r="O80" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P80" s="1" t="n">
+      <c r="Q80" s="1" t="n">
         <v>39394</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="R80" t="n">
         <v>2007</v>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="S80" t="n">
+      <c r="T80" t="n">
         <v>33</v>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7522,37 +7606,38 @@
           <t>9b</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
         <v>32</v>
       </c>
-      <c r="N81" t="b">
-        <v>0</v>
-      </c>
-      <c r="O81" t="inlineStr">
+      <c r="O81" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P81" s="1" t="n">
+      <c r="Q81" s="1" t="n">
         <v>41489</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="R81" t="n">
         <v>2013</v>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="S81" t="n">
+      <c r="T81" t="n">
         <v>33</v>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7610,37 +7695,38 @@
           <t>9b</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
         <is>
           <t>9a</t>
         </is>
       </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
         <v>31</v>
       </c>
-      <c r="N82" t="b">
-        <v>0</v>
-      </c>
-      <c r="O82" t="inlineStr">
+      <c r="O82" t="b">
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t>5.14d</t>
         </is>
       </c>
-      <c r="P82" s="1" t="n">
+      <c r="Q82" s="1" t="n">
         <v>42309</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="R82" t="n">
         <v>2015</v>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="S82" t="n">
+      <c r="T82" t="n">
         <v>33</v>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7698,37 +7784,38 @@
           <t>9b</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
         <v>32</v>
       </c>
-      <c r="N83" t="b">
-        <v>0</v>
-      </c>
-      <c r="O83" t="inlineStr">
+      <c r="O83" t="b">
+        <v>0</v>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P83" s="1" t="n">
+      <c r="Q83" s="1" t="n">
         <v>43703</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="R83" t="n">
         <v>2019</v>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="S83" t="n">
+      <c r="T83" t="n">
         <v>33</v>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7786,37 +7873,38 @@
           <t>9b</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
         <is>
           <t>9a+</t>
         </is>
       </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
         <v>32</v>
       </c>
-      <c r="N84" t="b">
-        <v>0</v>
-      </c>
-      <c r="O84" t="inlineStr">
+      <c r="O84" t="b">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr">
         <is>
           <t>5.15a</t>
         </is>
       </c>
-      <c r="P84" s="1" t="n">
+      <c r="Q84" s="1" t="n">
         <v>44231</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="R84" t="n">
         <v>2021</v>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="S84" t="n">
+      <c r="T84" t="n">
         <v>33</v>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -7874,37 +7962,38 @@
           <t>9b/9b+</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
         <is>
           <t>9b+</t>
         </is>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
         <v>34</v>
       </c>
-      <c r="N85" t="b">
-        <v>0</v>
-      </c>
-      <c r="O85" t="inlineStr">
+      <c r="O85" t="b">
+        <v>0</v>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>5.15c</t>
         </is>
       </c>
-      <c r="P85" s="1" t="n">
+      <c r="Q85" s="1" t="n">
         <v>44642</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="R85" t="n">
         <v>2022</v>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="S85" t="n">
+      <c r="T85" t="n">
         <v>33</v>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>upgrade</t>
         </is>
@@ -7962,37 +8051,38 @@
           <t>9b+</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
         <v>33</v>
       </c>
-      <c r="N86" t="b">
-        <v>0</v>
-      </c>
-      <c r="O86" t="inlineStr">
+      <c r="O86" t="b">
+        <v>0</v>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t>5.15b</t>
         </is>
       </c>
-      <c r="P86" s="1" t="n">
+      <c r="Q86" s="1" t="n">
         <v>44264</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="R86" t="n">
         <v>2021</v>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>9b+</t>
         </is>
       </c>
-      <c r="S86" t="n">
+      <c r="T86" t="n">
         <v>34</v>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
@@ -8050,37 +8140,131 @@
           <t>9b+</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="M87" t="n">
+      <c r="N87" t="n">
         <v>33</v>
       </c>
-      <c r="N87" t="b">
-        <v>0</v>
-      </c>
-      <c r="O87" t="inlineStr">
+      <c r="O87" t="b">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>5.15b</t>
         </is>
       </c>
-      <c r="P87" s="1" t="n">
+      <c r="Q87" s="1" t="n">
         <v>45013</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="R87" t="n">
         <v>2023</v>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>9b+</t>
         </is>
       </c>
-      <c r="S87" t="n">
+      <c r="T87" t="n">
         <v>34</v>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>downgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>466</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://climbing-history.org/climb/466</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Bibliographie</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>9b+</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Sport route</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Céüse</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>7</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Alex Megos</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Lead | worked</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>5th Aug 2020</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>9c</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>climbing-history.org/climb/466, climb description</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>9b+</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>34</v>
+      </c>
+      <c r="O88" t="b">
+        <v>0</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>5.15c</t>
+        </is>
+      </c>
+      <c r="Q88" s="1" t="n">
+        <v>44048</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2020</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>9c</t>
+        </is>
+      </c>
+      <c r="T88" t="n">
+        <v>35</v>
+      </c>
+      <c r="U88" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
